--- a/RMTest-9.xlsx
+++ b/RMTest-9.xlsx
@@ -124,12 +124,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF86A5A"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -144,7 +150,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -160,6 +166,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,19 +513,19 @@
         <v>5</v>
       </c>
       <c r="D2" s="3">
-        <v>4.991</v>
+        <v>4.957</v>
       </c>
       <c r="E2" s="1">
-        <v>-0.1</v>
+        <v>0</v>
       </c>
       <c r="F2" s="1">
         <v>0</v>
       </c>
       <c r="G2" s="3">
-        <v>4.962</v>
+        <v>5.011</v>
       </c>
       <c r="H2" s="4">
-        <v>0.002936</v>
+        <v>-0.005397</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -530,10 +539,10 @@
         <v>5</v>
       </c>
       <c r="D3" s="3">
-        <v>4.992</v>
+        <v>4.961</v>
       </c>
       <c r="E3" s="1">
-        <v>24.8</v>
+        <v>25.9</v>
       </c>
       <c r="F3" s="1">
         <v>0</v>
@@ -550,19 +559,19 @@
         <v>6.25</v>
       </c>
       <c r="D4" s="3">
-        <v>6.235</v>
+        <v>6.169</v>
       </c>
       <c r="E4" s="1">
         <v>49.8</v>
       </c>
       <c r="F4" s="1">
-        <v>25</v>
+        <v>23.9</v>
       </c>
       <c r="G4" s="3">
-        <v>6.232</v>
+        <v>6.215</v>
       </c>
       <c r="H4" s="4">
-        <v>0.000341</v>
+        <v>-0.004614</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -576,19 +585,19 @@
         <v>7.5</v>
       </c>
       <c r="D5" s="3">
-        <v>7.498</v>
+        <v>7.446</v>
       </c>
       <c r="E5" s="1">
-        <v>75</v>
+        <v>74.8</v>
       </c>
       <c r="F5" s="1">
-        <v>50.2</v>
+        <v>48.9</v>
       </c>
       <c r="G5" s="3">
-        <v>7.506</v>
+        <v>7.472</v>
       </c>
       <c r="H5" s="4">
-        <v>-0.000753</v>
+        <v>-0.002643</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -602,19 +611,19 @@
         <v>8.75</v>
       </c>
       <c r="D6" s="3">
-        <v>8.766999999999999</v>
+        <v>8.73</v>
       </c>
       <c r="E6" s="1">
-        <v>99.90000000000001</v>
+        <v>99.8</v>
       </c>
       <c r="F6" s="1">
-        <v>75.09999999999999</v>
+        <v>73.8</v>
       </c>
       <c r="G6" s="3">
-        <v>8.771000000000001</v>
+        <v>8.73</v>
       </c>
       <c r="H6" s="4">
-        <v>-0.000315</v>
+        <v>7.2E-05</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -631,16 +640,16 @@
         <v>9.999000000000001</v>
       </c>
       <c r="E7" s="1">
-        <v>124.2</v>
+        <v>125</v>
       </c>
       <c r="F7" s="1">
-        <v>99.40000000000001</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="G7" s="3">
         <v>10</v>
       </c>
       <c r="H7" s="4">
-        <v>-0.000116</v>
+        <v>-7.8E-05</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -648,7 +657,7 @@
         <v>14</v>
       </c>
       <c r="B8" s="1">
-        <v>165.4</v>
+        <v>165.5</v>
       </c>
       <c r="C8" s="2">
         <v>10</v>
@@ -657,10 +666,10 @@
         <v>9.999000000000001</v>
       </c>
       <c r="E8" s="1">
-        <v>165.4</v>
+        <v>165.5</v>
       </c>
       <c r="F8" s="1">
-        <v>140.6</v>
+        <v>139.6</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -674,10 +683,10 @@
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>4.992</v>
+        <v>4.955</v>
       </c>
       <c r="E9" s="1">
-        <v>-25.4</v>
+        <v>-24.5</v>
       </c>
       <c r="F9" s="1">
         <v>0</v>
@@ -694,19 +703,19 @@
         <v>3.75</v>
       </c>
       <c r="D10" s="3">
-        <v>3.73</v>
+        <v>3.696</v>
       </c>
       <c r="E10" s="1">
-        <v>-50.3</v>
+        <v>-50.1</v>
       </c>
       <c r="F10" s="1">
-        <v>-24.9</v>
+        <v>-25.6</v>
       </c>
       <c r="G10" s="3">
-        <v>3.702</v>
+        <v>3.723</v>
       </c>
       <c r="H10" s="4">
-        <v>0.002859</v>
+        <v>-0.002732</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -720,19 +729,19 @@
         <v>2.5</v>
       </c>
       <c r="D11" s="3">
-        <v>2.442</v>
+        <v>2.46</v>
       </c>
       <c r="E11" s="1">
         <v>-75.09999999999999</v>
       </c>
       <c r="F11" s="1">
-        <v>-49.7</v>
+        <v>-50.5</v>
       </c>
       <c r="G11" s="3">
-        <v>2.445</v>
+        <v>2.466</v>
       </c>
       <c r="H11" s="4">
-        <v>-0.000316</v>
+        <v>-0.00052</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -746,19 +755,19 @@
         <v>1.25</v>
       </c>
       <c r="D12" s="3">
-        <v>1.172</v>
+        <v>1.198</v>
       </c>
       <c r="E12" s="1">
-        <v>-100.1</v>
+        <v>-100</v>
       </c>
       <c r="F12" s="1">
-        <v>-74.7</v>
+        <v>-75.5</v>
       </c>
       <c r="G12" s="3">
-        <v>1.176</v>
+        <v>1.208</v>
       </c>
       <c r="H12" s="4">
-        <v>-0.000379</v>
+        <v>-0.001038</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -772,19 +781,19 @@
         <v>0</v>
       </c>
       <c r="D13" s="3">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="E13" s="1">
-        <v>-123.3</v>
+        <v>-124</v>
       </c>
       <c r="F13" s="1">
-        <v>-97.90000000000001</v>
+        <v>-99.5</v>
       </c>
       <c r="G13" s="3">
         <v>0</v>
       </c>
       <c r="H13" s="4">
-        <v>0.000109</v>
+        <v>3.3E-05</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -792,7 +801,7 @@
         <v>20</v>
       </c>
       <c r="B14" s="1">
-        <v>-165.4</v>
+        <v>-165.5</v>
       </c>
       <c r="C14" s="2">
         <v>0</v>
@@ -801,10 +810,10 @@
         <v>0</v>
       </c>
       <c r="E14" s="1">
-        <v>-165.4</v>
+        <v>-165.5</v>
       </c>
       <c r="F14" s="1">
-        <v>-140</v>
+        <v>-141</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -812,13 +821,13 @@
         <v>21</v>
       </c>
       <c r="B16" s="1">
-        <v>50.2</v>
+        <v>50.4</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="H16" s="4">
-        <v>0.002936</v>
+      <c r="H16" s="6">
+        <v>7.2E-05</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -826,13 +835,13 @@
         <v>22</v>
       </c>
       <c r="B17" s="1">
-        <v>99.40000000000001</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="H17" s="4">
-        <v>-0.000753</v>
+      <c r="H17" s="6">
+        <v>-0.005397</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -840,7 +849,7 @@
         <v>23</v>
       </c>
       <c r="B18" s="1">
-        <v>97.90000000000001</v>
+        <v>99.5</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -848,7 +857,7 @@
         <v>24</v>
       </c>
       <c r="B20" s="1">
-        <v>197.3</v>
+        <v>198.5</v>
       </c>
     </row>
   </sheetData>
